--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487748_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487748_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0716</v>
+        <v>5.2896</v>
       </c>
       <c r="E2" t="n">
         <v>2.6196</v>
       </c>
       <c r="F2" t="n">
-        <v>2.452</v>
+        <v>2.67</v>
       </c>
       <c r="G2" t="n">
         <v>2.8174</v>
@@ -610,13 +610,13 @@
         <v>1.5523</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.522</v>
+        <v>-0.3039</v>
       </c>
       <c r="T2" t="n">
         <v>0.0617</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5836</v>
+        <v>-0.3656</v>
       </c>
       <c r="V2" t="n">
         <v>1.2239</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7271</v>
+        <v>3.8187</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7759</v>
+        <v>2.2764</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9512</v>
+        <v>1.5424</v>
       </c>
       <c r="G3" t="n">
         <v>3.0863</v>
@@ -688,13 +688,13 @@
         <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3751</v>
+        <v>1.4667</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0617</v>
+        <v>0.5622</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3134</v>
+        <v>0.9046</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7343</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5245</v>
+        <v>3.7613</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8578</v>
+        <v>1.2582</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6667</v>
+        <v>2.5031</v>
       </c>
       <c r="G4" t="n">
         <v>3.0414</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1875</v>
+        <v>1.4244</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2445</v>
+        <v>0.6449</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9431</v>
+        <v>0.7795</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1224</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5309</v>
+        <v>2.3664</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.7177</v>
+        <v>-3.3183</v>
       </c>
       <c r="F5" t="n">
-        <v>5.2487</v>
+        <v>5.6847</v>
       </c>
       <c r="G5" t="n">
         <v>2.1902</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6736</v>
+        <v>1.5091</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6397</v>
+        <v>1.0391</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0339</v>
+        <v>0.47</v>
       </c>
       <c r="V5" t="n">
         <v>1.3836</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0225</v>
+        <v>0.4769</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4783</v>
+        <v>-0.7786</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5008</v>
+        <v>1.2555</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2412</v>
@@ -922,13 +922,13 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9637</v>
+        <v>0.4181</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4856</v>
+        <v>0.1853</v>
       </c>
       <c r="U6" t="n">
-        <v>0.478</v>
+        <v>0.2327</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8641</v>
+        <v>0.2101</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3798</v>
+        <v>-2.0884</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2439</v>
+        <v>2.2985</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3255</v>
+        <v>2.9209</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1458</v>
+        <v>2.2714</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4714</v>
+        <v>0.6495</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.4408</v>
+        <v>0.9915</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1853</v>
+        <v>1.0092</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.2555</v>
+        <v>-0.0178</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1153</v>
+        <v>1.9295</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3312</v>
+        <v>1.2622</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7841</v>
+        <v>0.6673</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5523</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2985</v>
+        <v>-3.1045</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9329</v>
+        <v>-0.1884</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.0247</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0211</v>
+        <v>-0.2131</v>
       </c>
       <c r="V7" t="n">
-        <v>1.809</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.338</v>
+        <v>-0.1537</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.688</v>
+        <v>-3.58</v>
       </c>
       <c r="F8" t="n">
-        <v>2.026</v>
+        <v>3.4263</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9209</v>
+        <v>-2.3255</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2714</v>
+        <v>0.1458</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6495</v>
+        <v>-2.4714</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9915</v>
+        <v>-3.4408</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0092</v>
+        <v>-0.1853</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0178</v>
+        <v>-3.2555</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9295</v>
+        <v>1.1153</v>
       </c>
       <c r="N8" t="n">
-        <v>1.2622</v>
+        <v>0.3312</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6673</v>
+        <v>0.7841</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.5224</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1045</v>
+        <v>-3.2985</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0606</v>
+        <v>1.9151</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4251</v>
+        <v>0.7116</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4856</v>
+        <v>1.2035</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.809</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8319</v>
+        <v>-1.2098</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3646</v>
+        <v>-5.0941</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4672</v>
+        <v>3.8843</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8111</v>
+        <v>0.5065</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7554999999999999</v>
+        <v>2.5425</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5666</v>
+        <v>-2.0359</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2323</v>
+        <v>-0.8091</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0618</v>
+        <v>2.4057</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2941</v>
+        <v>-3.2149</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4212</v>
+        <v>1.3156</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6937</v>
+        <v>0.1367</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2725</v>
+        <v>1.1789</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7761</v>
+        <v>-3.2985</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.194</v>
+        <v>-5.0448</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2909</v>
+        <v>0.715</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0617</v>
+        <v>0.7598</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3526</v>
+        <v>-0.0448</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.506</v>
+        <v>0.8672</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.506</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7014</v>
+        <v>-2.0142</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.0951</v>
+        <v>-1.765</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3937</v>
+        <v>-0.2492</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5065</v>
+        <v>-0.8111</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5425</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0359</v>
+        <v>-1.5666</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8091</v>
+        <v>-1.2323</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4057</v>
+        <v>0.0618</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.2149</v>
+        <v>-1.2941</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3156</v>
+        <v>0.4212</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1367</v>
+        <v>0.6937</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1789</v>
+        <v>-0.2725</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2985</v>
+        <v>0.7761</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.0448</v>
+        <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7766</v>
+        <v>-0.4733</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2412</v>
+        <v>-0.3387</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5354</v>
+        <v>-0.1346</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8672</v>
+        <v>-1.506</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.8672</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.5454</v>
+        <v>12.5453</v>
       </c>
       <c r="E11" t="n">
         <v>-10.4702</v>
       </c>
       <c r="F11" t="n">
-        <v>23.0158</v>
+        <v>23.0156</v>
       </c>
       <c r="G11" t="n">
         <v>11.1849</v>
@@ -1282,10 +1282,10 @@
         <v>14.5495</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3646</v>
+        <v>-3.364599999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6742</v>
+        <v>-0.6742000000000004</v>
       </c>
       <c r="K11" t="n">
         <v>9.2522</v>
@@ -1297,10 +1297,10 @@
         <v>11.8591</v>
       </c>
       <c r="N11" t="n">
-        <v>5.297400000000001</v>
+        <v>5.2974</v>
       </c>
       <c r="O11" t="n">
-        <v>6.5618</v>
+        <v>6.561800000000001</v>
       </c>
       <c r="P11" t="n">
         <v>-7.761200000000001</v>
@@ -1312,13 +1312,13 @@
         <v>10.672</v>
       </c>
       <c r="S11" t="n">
-        <v>6.482699999999999</v>
+        <v>6.4828</v>
       </c>
       <c r="T11" t="n">
         <v>3.6506</v>
       </c>
       <c r="U11" t="n">
-        <v>2.8323</v>
+        <v>2.8322</v>
       </c>
       <c r="V11" t="n">
         <v>2.6389</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6488</v>
+        <v>2.9853</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7986</v>
+        <v>0.5984</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8502</v>
+        <v>2.3869</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5659999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>2.5224</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2485</v>
+        <v>-0.415</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0584</v>
+        <v>-0.2586</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3069</v>
+        <v>-0.1564</v>
       </c>
       <c r="V12" t="n">
         <v>1.6379</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.818</v>
+        <v>1.4438</v>
       </c>
       <c r="E13" t="n">
-        <v>1.572</v>
+        <v>0.1706</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2459</v>
+        <v>1.2732</v>
       </c>
       <c r="G13" t="n">
         <v>1.8218</v>
@@ -1468,13 +1468,13 @@
         <v>2.3284</v>
       </c>
       <c r="S13" t="n">
-        <v>0.238</v>
+        <v>-1.1362</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2157</v>
+        <v>-0.1857</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9778</v>
+        <v>-0.9505</v>
       </c>
       <c r="V13" t="n">
         <v>0.5642</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>M. DEL VALLE REGALADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.0219</v>
+        <v>-1.1513</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2789</v>
+        <v>-1.7168</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2571</v>
+        <v>0.5655</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.426</v>
+        <v>-1.6057</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0428</v>
+        <v>-2.7657</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3832</v>
+        <v>1.1601</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2902</v>
+        <v>-1.2755</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0216</v>
+        <v>-1.2399</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3118</v>
+        <v>-0.0356</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1358</v>
+        <v>-0.3302</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0645</v>
+        <v>-1.5258</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9287</v>
+        <v>1.1956</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S14" t="n">
-        <v>0.602</v>
+        <v>-0.4756</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6695</v>
+        <v>-0.2473</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0675</v>
+        <v>-0.2282</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8098</v>
+        <v>-0.2343</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0919</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DEL VALLE REGALADO</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.8337</v>
+        <v>-1.3772</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3174</v>
+        <v>-1.8795</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4837</v>
+        <v>0.5024</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6057</v>
+        <v>-0.426</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.7657</v>
+        <v>-0.0428</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1601</v>
+        <v>-0.3832</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2755</v>
+        <v>-0.2902</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2399</v>
+        <v>1.0216</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0356</v>
+        <v>-1.3118</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3302</v>
+        <v>-0.1358</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5258</v>
+        <v>-1.0645</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1956</v>
+        <v>0.9287</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1642</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1579</v>
+        <v>0.2467</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8479</v>
+        <v>0.0689</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.31</v>
+        <v>0.1778</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2343</v>
+        <v>-0.8098</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2343</v>
+        <v>-1.0919</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8561</v>
+        <v>-1.8467</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.5309</v>
+        <v>-4.3307</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6748</v>
+        <v>2.484</v>
       </c>
       <c r="G16" t="n">
         <v>-4.7856</v>
@@ -1702,13 +1702,13 @@
         <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0368</v>
+        <v>-1.0274</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7863</v>
+        <v>-0.5861</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2505</v>
+        <v>-0.4413</v>
       </c>
       <c r="V16" t="n">
         <v>1.6379</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.8706</v>
+        <v>-2.1521</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.0379</v>
+        <v>-5.5374</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1673</v>
+        <v>3.3853</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2115</v>
@@ -1780,13 +1780,13 @@
         <v>3.1045</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2672</v>
+        <v>-1.5486</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1497</v>
+        <v>-0.6492</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1175</v>
+        <v>-0.8995</v>
       </c>
       <c r="V17" t="n">
         <v>0.414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1743</v>
+        <v>-3.0197</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.6883</v>
+        <v>-3.5882</v>
       </c>
       <c r="F18" t="n">
-        <v>0.514</v>
+        <v>0.5685</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4809</v>
@@ -1858,13 +1858,13 @@
         <v>2.5224</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4307</v>
+        <v>-1.2761</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6046</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.7716</v>
       </c>
       <c r="V18" t="n">
         <v>-2.5911</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7426</v>
+        <v>-3.2237</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.2365</v>
+        <v>-3.6359</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4939</v>
+        <v>0.4122</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3606</v>
@@ -1936,13 +1936,13 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1581</v>
+        <v>-0.6393</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9085</v>
+        <v>-0.3079</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2496</v>
+        <v>-0.3314</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6119</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5129</v>
+        <v>-4.2037</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2963</v>
+        <v>-3.0961</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2167</v>
+        <v>-1.1077</v>
       </c>
       <c r="G20" t="n">
         <v>-0.5705</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5206</v>
+        <v>-0.2114</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3623</v>
+        <v>-0.1621</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1584</v>
+        <v>-0.0493</v>
       </c>
       <c r="V20" t="n">
         <v>-2.6457</v>
@@ -2053,7 +2053,7 @@
         <v>-23.0156</v>
       </c>
       <c r="F21" t="n">
-        <v>10.4702</v>
+        <v>10.4703</v>
       </c>
       <c r="G21" t="n">
         <v>-11.185</v>
@@ -2092,13 +2092,13 @@
         <v>18.4331</v>
       </c>
       <c r="S21" t="n">
-        <v>-6.482799999999999</v>
+        <v>-6.482900000000001</v>
       </c>
       <c r="T21" t="n">
         <v>-2.8325</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.6505</v>
+        <v>-3.6504</v>
       </c>
       <c r="V21" t="n">
         <v>-2.638800000000001</v>
